--- a/Excel/RoleSelect.xlsx
+++ b/Excel/RoleSelect.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\42421\Desktop\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3140DA3D-0454-40A6-8186-B9154EF4D46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C0F876-D823-4283-A813-126049FB7ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -682,7 +682,7 @@
         <v>19</v>
       </c>
       <c r="J5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="1">
         <v>0.3</v>
@@ -715,7 +715,7 @@
         <v>18</v>
       </c>
       <c r="J6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>20</v>
       </c>
       <c r="J7" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" s="1">
         <v>0.5</v>

--- a/Excel/RoleSelect.xlsx
+++ b/Excel/RoleSelect.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\MightyFinalFight\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Unity\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C0F876-D823-4283-A813-126049FB7ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B2839B-9C63-450A-BDA2-CE879872EC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,27 +158,32 @@
     <t>Cody</t>
   </si>
   <si>
+    <t>headIcon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>头像</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Cody</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Guy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Guy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Hagger</t>
-  </si>
-  <si>
-    <t>headIcon</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>头像</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/Character/Cody</t>
-  </si>
-  <si>
-    <t>Icon/Character/Guy</t>
-  </si>
-  <si>
-    <t>Icon/Character/Hagger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icons/Hagger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -521,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.75" style="1" customWidth="1"/>
@@ -534,25 +539,23 @@
     <col min="9" max="9" width="25.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="22.25" style="1" customWidth="1"/>
     <col min="11" max="11" width="20.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="26.375" style="2" customWidth="1"/>
-    <col min="14" max="14" width="27.625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="24.625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="17" style="1" customWidth="1"/>
-    <col min="17" max="17" width="18.625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="27.75" style="1" customWidth="1"/>
-    <col min="19" max="19" width="37.875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="14.625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="21.5" style="1" customWidth="1"/>
-    <col min="22" max="22" width="20.375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="13.625" style="2" customWidth="1"/>
-    <col min="24" max="24" width="18.875" style="1" customWidth="1"/>
-    <col min="25" max="25" width="13" style="1" customWidth="1"/>
-    <col min="26" max="26" width="9" style="2"/>
-    <col min="27" max="16384" width="9" style="1"/>
+    <col min="12" max="12" width="27.625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="24.625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="17" style="1" customWidth="1"/>
+    <col min="15" max="15" width="18.625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="27.75" style="1" customWidth="1"/>
+    <col min="17" max="17" width="37.875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="14.625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="21.5" style="1" customWidth="1"/>
+    <col min="20" max="20" width="20.375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="13.625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="18.875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="13" style="1" customWidth="1"/>
+    <col min="24" max="24" width="9" style="2"/>
+    <col min="25" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -569,7 +572,7 @@
         <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
@@ -587,7 +590,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -622,7 +625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
@@ -636,7 +639,7 @@
         <v>29</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>7</v>
@@ -653,10 +656,10 @@
       <c r="K3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S3" s="4"/>
+      <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:21" ht="58.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" ht="58.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
         <v>1001</v>
       </c>
@@ -670,7 +673,7 @@
         <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>11</v>
@@ -687,9 +690,9 @@
       <c r="K5" s="1">
         <v>0.3</v>
       </c>
-      <c r="U5" s="3"/>
+      <c r="S5" s="3"/>
     </row>
-    <row r="6" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B6" s="1">
         <v>1002</v>
       </c>
@@ -697,13 +700,13 @@
         <v>1002</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>12</v>
@@ -720,9 +723,9 @@
       <c r="K6" s="1">
         <v>1</v>
       </c>
-      <c r="U6" s="3"/>
+      <c r="S6" s="3"/>
     </row>
-    <row r="7" spans="1:21" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
         <v>1003</v>
       </c>
@@ -730,7 +733,7 @@
         <v>1003</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>26</v>
@@ -753,7 +756,7 @@
       <c r="K7" s="1">
         <v>0.5</v>
       </c>
-      <c r="U7" s="3"/>
+      <c r="S7" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Excel/RoleSelect.xlsx
+++ b/Excel/RoleSelect.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Unity\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B2839B-9C63-450A-BDA2-CE879872EC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD37557E-6EB1-4E0D-8DDD-FF34B3C91F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -95,15 +95,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Sound/Jump</t>
-  </si>
-  <si>
-    <t>Sound/CodyBullet</t>
-  </si>
-  <si>
-    <t>Sound/HaggerRollingLong</t>
-  </si>
-  <si>
     <t>showTime</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -166,23 +157,35 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Icons/Cody</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Guy</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Icons/Guy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Hagger</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Icons/Hagger</t>
+    <t>Common/Cody.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Common/Guy.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Common/Hagger.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound/CodyBullet.ogg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound/Jump.ogg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound/HaggerRollingLong.ogg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -534,7 +537,7 @@
     <col min="3" max="4" width="13.25" style="1" customWidth="1"/>
     <col min="5" max="5" width="25.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="22.25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="9" width="25.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="22.25" style="1" customWidth="1"/>
@@ -566,13 +569,13 @@
         <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
@@ -584,10 +587,10 @@
         <v>17</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
@@ -633,13 +636,13 @@
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>7</v>
@@ -648,13 +651,13 @@
         <v>16</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="Q3" s="4"/>
     </row>
@@ -667,13 +670,13 @@
         <v>1001</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>11</v>
@@ -682,7 +685,7 @@
         <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="J5" s="1">
         <v>2</v>
@@ -700,13 +703,13 @@
         <v>1002</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>12</v>
@@ -715,7 +718,7 @@
         <v>14</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="J6" s="1">
         <v>2</v>
@@ -733,13 +736,13 @@
         <v>1003</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>13</v>
@@ -748,7 +751,7 @@
         <v>14</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J7" s="1">
         <v>2</v>

--- a/Excel/RoleSelect.xlsx
+++ b/Excel/RoleSelect.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Unity\MightyFinalFight\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD37557E-6EB1-4E0D-8DDD-FF34B3C91F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEE4C09-BA68-4365-A306-93395ACDD4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,15 +71,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CharacterUI/CodyUI</t>
-  </si>
-  <si>
-    <t>CharacterUI/GuyUI</t>
-  </si>
-  <si>
-    <t>CharacterUI/HaggerUI</t>
-  </si>
-  <si>
     <t>Show</t>
   </si>
   <si>
@@ -186,6 +177,18 @@
   </si>
   <si>
     <t>Sound/HaggerRollingLong.ogg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterUI/CodyUI.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterUI/GuyUI.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterUI/HaggerUI.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -569,28 +572,28 @@
         <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
@@ -636,28 +639,28 @@
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="Q3" s="4"/>
     </row>
@@ -670,22 +673,22 @@
         <v>1001</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="J5" s="1">
         <v>2</v>
@@ -703,22 +706,22 @@
         <v>1002</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="J6" s="1">
         <v>2</v>
@@ -736,22 +739,22 @@
         <v>1003</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="J7" s="1">
         <v>2</v>

--- a/Excel/RoleSelect.xlsx
+++ b/Excel/RoleSelect.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEE4C09-BA68-4365-A306-93395ACDD4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D83982-7F12-4D6C-A404-8DDDE2DACF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2595" yWindow="2595" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
   <si>
     <t>SheetName</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -106,21 +106,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>THE HOT-TEMPERED WRESTLER AND MAYOR
-OF METRO CITY.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DESCENDED FROM NINJA,HE POSSESSES
-INCREDIBLE AGILITY.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A TOUGH STREET FIGHTER WHO IS
-SKILLED WITH KNIVES.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>描述</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -137,23 +122,12 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Cody</t>
-  </si>
-  <si>
     <t>headIcon</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>头像</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Guy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hagger</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Common/Cody.png</t>
@@ -537,12 +511,13 @@
   <cols>
     <col min="1" max="1" width="14.75" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
-    <col min="3" max="4" width="13.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="25.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="22.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="27.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="20" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="29.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="22.25" style="1" customWidth="1"/>
     <col min="11" max="11" width="20.625" style="1" customWidth="1"/>
     <col min="12" max="12" width="27.625" style="2" customWidth="1"/>
@@ -572,13 +547,13 @@
         <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
@@ -607,10 +582,10 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>4</v>
@@ -639,13 +614,13 @@
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>7</v>
@@ -665,30 +640,30 @@
       <c r="Q3" s="4"/>
     </row>
     <row r="4" spans="1:19" ht="58.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
         <v>1001</v>
       </c>
       <c r="C5" s="1">
         <v>1001</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>22</v>
+      <c r="D5" s="1">
+        <v>1002</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1005</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J5" s="1">
         <v>2</v>
@@ -698,30 +673,30 @@
       </c>
       <c r="S5" s="3"/>
     </row>
-    <row r="6" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1">
         <v>1002</v>
       </c>
       <c r="C6" s="1">
         <v>1002</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>21</v>
+      <c r="D6" s="1">
+        <v>1003</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1006</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J6" s="1">
         <v>2</v>
@@ -731,30 +706,30 @@
       </c>
       <c r="S6" s="3"/>
     </row>
-    <row r="7" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
         <v>1003</v>
       </c>
       <c r="C7" s="1">
         <v>1003</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>20</v>
+      <c r="D7" s="1">
+        <v>1004</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1007</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J7" s="1">
         <v>2</v>

--- a/Excel/RoleSelect.xlsx
+++ b/Excel/RoleSelect.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D83982-7F12-4D6C-A404-8DDDE2DACF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D49773B5-FD7E-4042-871A-1911EBD0C871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="2595" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
   <si>
     <t>SheetName</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -163,6 +163,30 @@
   </si>
   <si>
     <t>CharacterUI/HaggerUI.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoleNameCody</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoleNameGuy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoleNameHagger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoleDescCody</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoleDescGuy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoleDescHagger</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -582,10 +606,10 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>4</v>
@@ -647,11 +671,11 @@
       <c r="C5" s="1">
         <v>1001</v>
       </c>
-      <c r="D5" s="1">
-        <v>1002</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1005</v>
+      <c r="D5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>26</v>
@@ -680,11 +704,11 @@
       <c r="C6" s="1">
         <v>1002</v>
       </c>
-      <c r="D6" s="1">
-        <v>1003</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1006</v>
+      <c r="D6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>27</v>
@@ -713,11 +737,11 @@
       <c r="C7" s="1">
         <v>1003</v>
       </c>
-      <c r="D7" s="1">
-        <v>1004</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1007</v>
+      <c r="D7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>28</v>

--- a/Excel/RoleSelect.xlsx
+++ b/Excel/RoleSelect.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MightyFinalFight\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Work\Unity\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D49773B5-FD7E-4042-871A-1911EBD0C871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{934099BB-589F-40A3-9E41-38464B386F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="RoleSelect" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
